--- a/tests/workbooktests/workbooks/test_options.xlsx
+++ b/tests/workbooktests/workbooks/test_options.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA4B6A2-F5C2-4EEF-B839-05CFED5D70DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3057C8F3-C357-4E09-8604-D61453A0B2E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" tabRatio="704" activeTab="7" xr2:uid="{CCFA635F-0F53-474D-82D2-FB064D5998FA}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" tabRatio="704" xr2:uid="{CCFA635F-0F53-474D-82D2-FB064D5998FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Market data" sheetId="1" r:id="rId1"/>
@@ -43,17 +43,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -62,14 +51,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -1060,7 +1049,7 @@
     <numFmt numFmtId="164" formatCode="0.00000000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1145,7 +1134,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1478,13 +1467,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63553D58-0814-44B3-9512-FB88DAAB633A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1481,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1501,25 +1490,25 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
+      <c r="B4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
+      <c r="B5" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
         <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1528,7 +1517,7 @@
         <v>欣[test_options.xlsx]Market data!R7C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1536,7 +1525,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1553,17 +1542,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A3E2BE9-54CB-4D98-8EEB-444D7357A4BF}">
   <dimension ref="A1:J86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="27.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="7" width="19.44140625" customWidth="1"/>
+    <col min="6" max="7" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1571,7 +1560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1588,7 +1577,7 @@
         <v>欣[test_options.xlsx]Heston engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -1597,7 +1586,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1606,12 +1595,12 @@
         <v>欣[test_options.xlsx]Heston engines!R5C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="G7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="G8" s="2" t="str" cm="1">
         <f t="array" ref="G8">_xll.qlTimeGridFromTimes(H8:I8)</f>
         <v>欣[test_options.xlsx]Heston engines!R8C7TimeGrid,A</v>
@@ -1623,7 +1612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>103</v>
       </c>
@@ -1639,7 +1628,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -1673,7 +1662,7 @@
         <v>0.39716005835063128</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>105</v>
       </c>
@@ -1707,7 +1696,7 @@
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>106</v>
       </c>
@@ -1741,7 +1730,7 @@
         <v>1.3901714719854346</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>107</v>
       </c>
@@ -1775,7 +1764,7 @@
         <v>-0.3506856326404631</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -1783,7 +1772,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" s="10" t="s">
         <v>110</v>
       </c>
@@ -1799,7 +1788,7 @@
         <v>欣[test_options.xlsx]Heston engines!R15C5HestonProcess,A</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="10" t="s">
         <v>111</v>
       </c>
@@ -1808,7 +1797,7 @@
         <v>欣[test_options.xlsx]Heston engines!R16C2HestonModel,A</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15">
       <c r="A18" s="10" t="s">
         <v>119</v>
       </c>
@@ -1817,7 +1806,7 @@
         <v>欣[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15">
       <c r="A19" s="10" t="s">
         <v>120</v>
       </c>
@@ -1825,7 +1814,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -1834,7 +1823,7 @@
         <v>0.19504877171446253</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1843,7 +1832,7 @@
         <v>0.39716005835063128</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>105</v>
       </c>
@@ -1852,7 +1841,7 @@
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -1861,7 +1850,7 @@
         <v>1.3901714719854346</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>107</v>
       </c>
@@ -1870,7 +1859,7 @@
         <v>-0.3506856326404631</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -1878,7 +1867,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -1892,7 +1881,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>127</v>
       </c>
@@ -1904,7 +1893,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -1918,12 +1907,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -1940,12 +1929,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="15">
       <c r="A33" s="10" t="s">
         <v>132</v>
       </c>
@@ -1974,7 +1963,7 @@
         <v>欣[test_options.xlsx]Heston engines!R33C7AnalyticHestonEngine,A</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -2003,7 +1992,7 @@
         <v>欣[test_options.xlsx]Heston engines!R34C7VanillaOption,A</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -2032,7 +2021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2061,12 +2050,12 @@
         <v>12.287102932994685</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>134</v>
       </c>
@@ -2074,7 +2063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>135</v>
       </c>
@@ -2082,7 +2071,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15">
       <c r="A42" s="10" t="s">
         <v>136</v>
       </c>
@@ -2095,7 +2084,7 @@
         <v>欣[test_options.xlsx]Heston engines!R42C3COSHestonEngine,A</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -2108,7 +2097,7 @@
         <v>欣[test_options.xlsx]Heston engines!R43C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -2121,7 +2110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2134,12 +2123,12 @@
         <v>12.286841497841706</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>138</v>
       </c>
@@ -2147,7 +2136,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>139</v>
       </c>
@@ -2155,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>140</v>
       </c>
@@ -2163,7 +2152,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="15">
       <c r="A51" s="10" t="s">
         <v>142</v>
       </c>
@@ -2176,7 +2165,7 @@
         <v>欣[test_options.xlsx]Heston engines!R51C3ExponentialFittingHestonEngine,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -2189,7 +2178,7 @@
         <v>欣[test_options.xlsx]Heston engines!R52C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -2202,7 +2191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -2215,12 +2204,12 @@
         <v>12.287050480685576</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>144</v>
       </c>
@@ -2228,7 +2217,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -2236,7 +2225,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="15">
       <c r="A60" s="10" t="s">
         <v>146</v>
       </c>
@@ -2249,7 +2238,7 @@
         <v>欣[test_options.xlsx]Heston engines!R60C3AnalyticPDFHestonEngine,A</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -2262,7 +2251,7 @@
         <v>欣[test_options.xlsx]Heston engines!R61C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -2275,7 +2264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -2288,12 +2277,12 @@
         <v>12.284270455453564</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>121</v>
       </c>
@@ -2301,7 +2290,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="15">
       <c r="A67" s="10" t="s">
         <v>148</v>
       </c>
@@ -2314,7 +2303,7 @@
         <v>欣[test_options.xlsx]Heston engines!R67C3AnalyticHestonForwardEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -2327,7 +2316,7 @@
         <v>欣[test_options.xlsx]Heston engines!R68C3ForwardVanillaOption,A</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>62</v>
       </c>
@@ -2340,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>44</v>
       </c>
@@ -2353,7 +2342,7 @@
         <v>4.5898111736183091</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>150</v>
       </c>
@@ -2362,12 +2351,12 @@
         <v>欣[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="A75" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>121</v>
       </c>
@@ -2375,7 +2364,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>122</v>
       </c>
@@ -2389,7 +2378,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>127</v>
       </c>
@@ -2401,7 +2390,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>123</v>
       </c>
@@ -2415,12 +2404,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>125</v>
       </c>
@@ -2437,12 +2426,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="15">
       <c r="A83" s="10" t="s">
         <v>151</v>
       </c>
@@ -2471,7 +2460,7 @@
         <v>欣[test_options.xlsx]Heston engines!R83C7AnalyticPTDHestonEngine,A</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -2500,7 +2489,7 @@
         <v>欣[test_options.xlsx]Heston engines!R84C7VanillaOption,A</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>62</v>
       </c>
@@ -2529,7 +2518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>44</v>
       </c>
@@ -2566,9 +2555,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA797EBA-DB93-4B2B-A0B5-515557004D82}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="5" t="s">
         <v>152</v>
       </c>
@@ -2581,18 +2570,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57BCD99C-6CC8-4FAC-BF2B-6F0D3D8F7291}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.375" customWidth="1"/>
+    <col min="3" max="3" width="28.125" customWidth="1"/>
+    <col min="5" max="5" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.375" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -2600,7 +2589,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2608,7 +2597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2623,7 +2612,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="E4" t="s">
         <v>156</v>
       </c>
@@ -2640,7 +2629,7 @@
         <v>9.3290904161635009</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2664,7 +2653,7 @@
         <v>9.3711357344708155</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2688,7 +2677,7 @@
         <v>9.4027356145560752</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2712,7 +2701,7 @@
         <v>9.2609572274678467</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2736,7 +2725,7 @@
         <v>9.2609101105709879</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="E9" t="s">
         <v>161</v>
       </c>
@@ -2753,7 +2742,7 @@
         <v>9.3679277555251854</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>163</v>
       </c>
@@ -2777,7 +2766,7 @@
         <v>9.3293601887633315</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>154</v>
       </c>
@@ -2785,7 +2774,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -2802,13 +2791,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48683ADB-9A1F-49AF-A07D-0818DEAE7B0D}">
   <dimension ref="A1:C157"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.109375" customWidth="1"/>
-    <col min="2" max="3" width="30.21875" customWidth="1"/>
+    <col min="1" max="1" width="34.125" customWidth="1"/>
+    <col min="2" max="3" width="30.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -2816,7 +2805,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2824,16 +2813,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="str" cm="1">
+      <c r="B3" t="str">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2842,7 +2831,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2851,25 +2840,25 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="str" cm="1">
+      <c r="B7" t="str">
         <f t="array" ref="B7">_xll.qlEuropeanExercise(B6)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R7C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="str" cm="1">
+      <c r="B8" t="str">
         <f t="array" ref="B8">_xll.qlAmericanExercise(B5,B6)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -2878,7 +2867,7 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="B11" s="3" t="s">
         <v>90</v>
       </c>
@@ -2886,7 +2875,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="B12" s="1">
         <f>EvaluationDate+90</f>
         <v>46264</v>
@@ -2896,7 +2885,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="B13">
         <v>1.5</v>
       </c>
@@ -2904,25 +2893,25 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15">
       <c r="A14" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="13" t="str" cm="1">
+      <c r="B14" s="13" t="str">
         <f t="array" ref="B14">_xll.qlFixedDividend(B13,B12)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R14C2FixedDividend,A</v>
       </c>
-      <c r="C14" s="13" t="str" cm="1">
+      <c r="C14" s="13" t="str">
         <f t="array" ref="C14">_xll.qlFixedDividend(C13,C12)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R14C3FixedDividend,A</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>177</v>
       </c>
@@ -2930,7 +2919,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>105</v>
       </c>
@@ -2938,7 +2927,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>178</v>
       </c>
@@ -2946,25 +2935,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="15">
       <c r="A20" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="2" t="str" cm="1">
+      <c r="B20" s="2" t="str">
         <f t="array" ref="B20">_xll.qlFdmSchemeDesc()</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R20C2FdmSchemeDesc,A</v>
       </c>
-      <c r="C20" s="2" t="str" cm="1">
+      <c r="C20" s="2" t="str">
         <f t="array" ref="C20">_xll.qlFdmSchemeDesc(C17,C18,C19)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>181</v>
       </c>
@@ -2973,25 +2962,25 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>182</v>
       </c>
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlFlatForward(EvaluationDate,0.04)</f>
+      <c r="B24" t="str">
+        <f>_xll.qlFlatForward(EvaluationDate,0.04,"actual365fixed")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R24C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>183</v>
       </c>
-      <c r="B25" t="str" cm="1">
+      <c r="B25" t="str">
         <f t="array" ref="B25">_xll.qlBlackConstantVol(EvaluationDate,"NullCalendar",0.15,"Act/365")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R25C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>184</v>
       </c>
@@ -2999,7 +2988,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>186</v>
       </c>
@@ -3007,23 +2996,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="15">
       <c r="A28" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="B28" t="str" cm="1">
+      <c r="B28" t="str">
         <f t="array" ref="B28">_xll.qlFdmQuantoHelper(B23,B24,B25,B26,B27)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>164</v>
       </c>
@@ -3036,12 +3025,12 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>166</v>
       </c>
@@ -3050,7 +3039,7 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>167</v>
       </c>
@@ -3058,7 +3047,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>168</v>
       </c>
@@ -3066,7 +3055,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>169</v>
       </c>
@@ -3074,7 +3063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>170</v>
       </c>
@@ -3083,7 +3072,7 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -3091,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -3099,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>173</v>
       </c>
@@ -3107,53 +3096,53 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="15">
       <c r="A42" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="2" t="str" cm="1">
+      <c r="B42" s="2" t="str">
         <f t="array" ref="B42">_xll.qlFdBlackScholesVanillaEngine(B32)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R42C2FdBlackScholesVanillaEngine,A</v>
       </c>
-      <c r="C42" s="2" t="str" cm="1">
+      <c r="C42" s="2" t="str">
         <f t="array" ref="C42">_xll.qlFdBlackScholesVanillaEngine(C32,$B$14:$C$14,C34,C35,C36,C37,C38,C39,C40,C41)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R42C3FdBlackScholesVanillaEngine,A</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="2" t="str" cm="1">
+      <c r="B43" s="2" t="str">
         <f t="array" ref="B43">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R43C2VanillaOption,A</v>
       </c>
-      <c r="C43" s="2" t="str" cm="1">
+      <c r="C43" s="2" t="str">
         <f t="array" ref="C43">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R43C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44" cm="1">
+      <c r="B44">
         <f t="array" ref="B44">_xll.qlInstrumentNPV(B43,_xll.qlInstrumentSetPricingEngine(B43,B42))</f>
         <v>9.3429764718916672</v>
       </c>
-      <c r="C44" cm="1">
+      <c r="C44">
         <f t="array" ref="C44">_xll.qlInstrumentNPV(C43,_xll.qlInstrumentSetPricingEngine(C43,C42))</f>
         <v>9.7832401815424106</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>164</v>
       </c>
@@ -3166,12 +3155,12 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>167</v>
       </c>
@@ -3179,7 +3168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>168</v>
       </c>
@@ -3187,7 +3176,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>169</v>
       </c>
@@ -3195,7 +3184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>170</v>
       </c>
@@ -3204,66 +3193,66 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="15">
       <c r="A54" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B54" s="2" t="str" cm="1">
+      <c r="B54" s="2" t="str">
         <f t="array" ref="B54">_xll.qlFdBlackScholesShoutEngine(B48)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R54C2FdBlackScholesShoutEngine,A</v>
       </c>
-      <c r="C54" s="2" t="str" cm="1">
+      <c r="C54" s="2" t="str">
         <f t="array" ref="C54">_xll.qlFdBlackScholesShoutEngine(C48,B14:C14,C50,C51,C52,C53)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R54C3FdBlackScholesShoutEngine,A</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="2" t="str" cm="1">
+      <c r="B55" s="2" t="str">
         <f t="array" ref="B55">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R55C2VanillaOption,A</v>
       </c>
-      <c r="C55" s="2" t="str" cm="1">
+      <c r="C55" s="2" t="str">
         <f t="array" ref="C55">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R55C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>44</v>
       </c>
-      <c r="B56" cm="1">
+      <c r="B56">
         <f t="array" ref="B56">_xll.qlInstrumentNPV(B55,_xll.qlInstrumentSetPricingEngine(B55,B54))</f>
         <v>11.867258968306036</v>
       </c>
-      <c r="C56" cm="1">
+      <c r="C56">
         <f t="array" ref="C56">_xll.qlInstrumentNPV(C55,_xll.qlInstrumentSetPricingEngine(C55,C54))</f>
         <v>13.185546860877</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="2" t="str" cm="1">
+      <c r="B60" s="2" t="str">
         <f t="array" ref="B60">_xll.qlOrnsteinUhlenbeckProcess(0.03,25,100,100)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R60C2OrnsteinUhlenbeckProcess,A</v>
       </c>
-      <c r="C60" s="2" t="str" cm="1">
+      <c r="C60" s="2" t="str">
         <f t="array" ref="C60">_xll.qlOrnsteinUhlenbeckProcess(0.03,25,100,100)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R60C3OrnsteinUhlenbeckProcess,A</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -3276,12 +3265,12 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>167</v>
       </c>
@@ -3289,7 +3278,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>168</v>
       </c>
@@ -3297,7 +3286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>169</v>
       </c>
@@ -3305,7 +3294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>191</v>
       </c>
@@ -3313,7 +3302,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>170</v>
       </c>
@@ -3322,51 +3311,51 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="15">
       <c r="A68" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B68" s="2" t="str" cm="1">
+      <c r="B68" s="2" t="str">
         <f t="array" ref="B68">_xll.qlFdOrnsteinUhlenbeckVanillaEngine(B60,B61)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R68C2FdOrnsteinUhlenbeckVanillaEngine,A</v>
       </c>
-      <c r="C68" s="2" t="str" cm="1">
+      <c r="C68" s="2" t="str">
         <f t="array" ref="C68">_xll.qlFdOrnsteinUhlenbeckVanillaEngine(C60,C61,B14:C14,C63,C64,C65,C66,C67)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R68C3FdOrnsteinUhlenbeckVanillaEngine,A</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="2" t="str" cm="1">
+      <c r="B69" s="2" t="str">
         <f t="array" ref="B69">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R69C2VanillaOption,A</v>
       </c>
-      <c r="C69" s="2" t="str" cm="1">
+      <c r="C69" s="2" t="str">
         <f t="array" ref="C69">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R69C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>44</v>
       </c>
-      <c r="B70" cm="1">
+      <c r="B70">
         <f t="array" ref="B70">_xll.qlInstrumentNPV(B69,_xll.qlInstrumentSetPricingEngine(B69,B68))</f>
         <v>9.6644350836594306</v>
       </c>
-      <c r="C70" cm="1">
+      <c r="C70">
         <f t="array" ref="C70">_xll.qlInstrumentNPV(C69,_xll.qlInstrumentSetPricingEngine(C69,C68))</f>
         <v>9.6639468353291189</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="A73" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>103</v>
       </c>
@@ -3374,7 +3363,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>104</v>
       </c>
@@ -3382,7 +3371,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>105</v>
       </c>
@@ -3390,7 +3379,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>106</v>
       </c>
@@ -3398,7 +3387,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>107</v>
       </c>
@@ -3406,7 +3395,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>193</v>
       </c>
@@ -3414,7 +3403,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>194</v>
       </c>
@@ -3422,7 +3411,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>195</v>
       </c>
@@ -3430,41 +3419,41 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="15">
       <c r="A82" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B82" t="str" cm="1">
+      <c r="B82" t="str">
         <f t="array" ref="B82">_xll.qlBatesProcess(DiscountCurve,DividendCurve,InitialValueS0,B74,B75,B76,B77,B78,B79,B80,B81)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R82C2BatesProcess,A</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
-      <c r="B85" s="2" t="str" cm="1">
+      <c r="B85" s="2" t="str">
         <f t="array" ref="B85">_xll.qlBatesModel($B$82)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R85C2BatesModel,A</v>
       </c>
-      <c r="C85" s="2" t="str" cm="1">
+      <c r="C85" s="2" t="str">
         <f t="array" ref="C85">_xll.qlBatesModel($B$82)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R85C3BatesModel,A</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -3472,7 +3461,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>168</v>
       </c>
@@ -3480,7 +3469,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>199</v>
       </c>
@@ -3488,7 +3477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>169</v>
       </c>
@@ -3496,7 +3485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>170</v>
       </c>
@@ -3505,46 +3494,46 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="15">
       <c r="A92" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B92" s="2" t="str" cm="1">
+      <c r="B92" s="2" t="str">
         <f t="array" ref="B92">_xll.qlFdBatesVanillaEngine(B85)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R92C2FdBatesVanillaEngine,A</v>
       </c>
-      <c r="C92" s="2" t="str" cm="1">
+      <c r="C92" s="2" t="str">
         <f t="array" ref="C92">_xll.qlFdBatesVanillaEngine(C85,B14:C14,C87,C88,C89,C90,C91)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R92C3FdBatesVanillaEngine,A</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>20</v>
       </c>
-      <c r="B93" s="2" t="str" cm="1">
+      <c r="B93" s="2" t="str">
         <f t="array" ref="B93">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R93C2VanillaOption,A</v>
       </c>
-      <c r="C93" s="2" t="str" cm="1">
+      <c r="C93" s="2" t="str">
         <f t="array" ref="C93">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R93C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>44</v>
       </c>
-      <c r="B94" cm="1">
+      <c r="B94">
         <f t="array" ref="B94">_xll.qlInstrumentNPV(B93,_xll.qlInstrumentSetPricingEngine(B93,B92))</f>
         <v>7.4042551002060373</v>
       </c>
-      <c r="C94" cm="1">
+      <c r="C94">
         <f t="array" ref="C94">_xll.qlInstrumentNPV(C93,_xll.qlInstrumentSetPricingEngine(C93,C92))</f>
         <v>8.742691884486387</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>103</v>
       </c>
@@ -3552,7 +3541,7 @@
         <v>0.19504877171446253</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>104</v>
       </c>
@@ -3560,7 +3549,7 @@
         <v>0.39716005835063128</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>105</v>
       </c>
@@ -3568,7 +3557,7 @@
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>106</v>
       </c>
@@ -3576,7 +3565,7 @@
         <v>1.3901714719854346</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -3584,7 +3573,7 @@
         <v>-0.3506856326404631</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>108</v>
       </c>
@@ -3592,41 +3581,41 @@
         <v>109</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="15">
       <c r="A103" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B103" t="str" cm="1">
+      <c r="B103" t="str">
         <f t="array" ref="B103">_xll.qlHestonProcess(DiscountCurve,DividendCurve,InitialValueS0,B97,B98,B99,B100,B101,B102)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R103C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>201</v>
       </c>
-      <c r="B107" s="2" t="str" cm="1">
+      <c r="B107" s="2" t="str">
         <f t="array" ref="B107">_xll.qlHestonModel($B$103)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R107C2HestonModel,A</v>
       </c>
-      <c r="C107" s="2" t="str" cm="1">
+      <c r="C107" s="2" t="str">
         <f t="array" ref="C107">_xll.qlHestonModel($B$103)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R107C3HestonModel,A</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>166</v>
       </c>
@@ -3635,7 +3624,7 @@
         <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>167</v>
       </c>
@@ -3643,7 +3632,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>168</v>
       </c>
@@ -3651,7 +3640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>199</v>
       </c>
@@ -3659,7 +3648,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>169</v>
       </c>
@@ -3667,25 +3656,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>170</v>
       </c>
-      <c r="C114" s="2" t="str" cm="1">
+      <c r="C114" s="2" t="str">
         <f t="array" ref="C114">_xll.qlFdmSchemeDescByName("Douglas")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R114C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>202</v>
       </c>
-      <c r="C115" s="2" t="str" cm="1">
+      <c r="C115" s="2" t="str">
         <f t="array" ref="C115">_xll.qlLocalConstantVol(EvaluationDate,1.1,"Act/365")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R115C3LocalVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>203</v>
       </c>
@@ -3693,53 +3682,53 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="15">
       <c r="A117" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B117" s="2" t="str" cm="1">
+      <c r="B117" s="2" t="str">
         <f t="array" ref="B117">_xll.qlFdHestonVanillaEngine(B107)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R117C2FdHestonVanillaEngine,A</v>
       </c>
-      <c r="C117" s="2" t="str" cm="1">
+      <c r="C117" s="2" t="str">
         <f t="array" ref="C117">_xll.qlFdHestonVanillaEngine(C107,B14:C14,C109,C110,C111,C112,C113,C114,C115,C116)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R117C3FdHestonVanillaEngine,A</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>20</v>
       </c>
-      <c r="B118" s="2" t="str" cm="1">
+      <c r="B118" s="2" t="str">
         <f t="array" ref="B118">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R118C2VanillaOption,A</v>
       </c>
-      <c r="C118" s="2" t="str" cm="1">
+      <c r="C118" s="2" t="str">
         <f t="array" ref="C118">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R118C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>44</v>
       </c>
-      <c r="B119" cm="1">
+      <c r="B119">
         <f t="array" ref="B119">_xll.qlInstrumentNPV(B118,_xll.qlInstrumentSetPricingEngine(B118,B117))</f>
         <v>11.497632140022677</v>
       </c>
-      <c r="C119" cm="1">
+      <c r="C119">
         <f t="array" ref="C119">_xll.qlInstrumentNPV(C118,_xll.qlInstrumentSetPricingEngine(C118,C117))</f>
         <v>15.674968871040523</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>205</v>
       </c>
@@ -3750,7 +3739,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>140</v>
       </c>
@@ -3761,7 +3750,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>206</v>
       </c>
@@ -3772,7 +3761,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>2</v>
       </c>
@@ -3785,7 +3774,7 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>167</v>
       </c>
@@ -3793,7 +3782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>168</v>
       </c>
@@ -3801,7 +3790,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>169</v>
       </c>
@@ -3809,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>207</v>
       </c>
@@ -3817,7 +3806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>191</v>
       </c>
@@ -3825,62 +3814,62 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>170</v>
       </c>
-      <c r="C132" s="2" t="str" cm="1">
+      <c r="C132" s="2" t="str">
         <f t="array" ref="C132">_xll.qlFdmSchemeDescByName("Douglas")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R132C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="15">
       <c r="A133" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B133" s="2" t="str" cm="1">
+      <c r="B133" s="2" t="str">
         <f t="array" ref="B133">_xll.qlFdCEVVanillaEngine(B123,B124,B125,B126)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R133C2FdCEVVanillaEngine,A</v>
       </c>
-      <c r="C133" s="2" t="str" cm="1">
+      <c r="C133" s="2" t="str">
         <f t="array" ref="C133">_xll.qlFdCEVVanillaEngine(C123,C124,C125,C126,C127,C128,C129,C130,C131,C132)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R133C3FdCEVVanillaEngine,A</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>20</v>
       </c>
-      <c r="B134" s="2" t="str" cm="1">
+      <c r="B134" s="2" t="str">
         <f t="array" ref="B134">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R134C2VanillaOption,A</v>
       </c>
-      <c r="C134" s="2" t="str" cm="1">
+      <c r="C134" s="2" t="str">
         <f t="array" ref="C134">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R134C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>44</v>
       </c>
-      <c r="B135" cm="1">
+      <c r="B135">
         <f t="array" ref="B135">_xll.qlInstrumentNPV(B134,_xll.qlInstrumentSetPricingEngine(B134,B133))</f>
-        <v>6.1465951688562654</v>
-      </c>
-      <c r="C135" cm="1">
+        <v>6.1465951688563498</v>
+      </c>
+      <c r="C135">
         <f t="array" ref="C135">_xll.qlInstrumentNPV(C134,_xll.qlInstrumentSetPricingEngine(C134,C133))</f>
         <v>6.136388290677278</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>205</v>
       </c>
@@ -3891,7 +3880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -3902,7 +3891,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>206</v>
       </c>
@@ -3913,7 +3902,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>194</v>
       </c>
@@ -3924,7 +3913,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>107</v>
       </c>
@@ -3935,7 +3924,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>2</v>
       </c>
@@ -3948,7 +3937,7 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>167</v>
       </c>
@@ -3956,7 +3945,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>210</v>
       </c>
@@ -3964,7 +3953,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>168</v>
       </c>
@@ -3972,7 +3961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>169</v>
       </c>
@@ -3980,7 +3969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>207</v>
       </c>
@@ -3988,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
         <v>191</v>
       </c>
@@ -3996,55 +3985,55 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>170</v>
       </c>
-      <c r="C151" s="2" t="str" cm="1">
+      <c r="C151" s="2" t="str">
         <f t="array" ref="C151">_xll.qlFdmSchemeDescByName("Douglas")</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R151C3FdmSchemeDesc,A</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="15">
       <c r="A152" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B152" s="2" t="str" cm="1">
+      <c r="B152" s="2" t="str">
         <f t="array" ref="B152">_xll.qlFdSabrVanillaEngine(B139,B140,B141,B142,B143,B144)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R152C2FdSabrVanillaEngine,A</v>
       </c>
-      <c r="C152" s="2" t="str" cm="1">
+      <c r="C152" s="2" t="str">
         <f t="array" ref="C152">_xll.qlFdSabrVanillaEngine(C139,C140,C141,C142,C143,C144,C145,C146,C147,C148,C149,C150,C151)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R152C3FdSabrVanillaEngine,A</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>20</v>
       </c>
-      <c r="B153" s="2" t="str" cm="1">
+      <c r="B153" s="2" t="str">
         <f t="array" ref="B153">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R153C2VanillaOption,A</v>
       </c>
-      <c r="C153" s="2" t="str" cm="1">
+      <c r="C153" s="2" t="str">
         <f t="array" ref="C153">_xll.qlVanillaOption($B$3,$B$9)</f>
         <v>欣[test_options.xlsx]Finite Difference engines!R153C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
         <v>44</v>
       </c>
-      <c r="B154" cm="1">
+      <c r="B154">
         <f t="array" ref="B154">_xll.qlInstrumentNPV(B153,_xll.qlInstrumentSetPricingEngine(B153,B152))</f>
-        <v>6.1551198442651627</v>
-      </c>
-      <c r="C154" cm="1">
+        <v>6.1551198442651431</v>
+      </c>
+      <c r="C154">
         <f t="array" ref="C154">_xll.qlInstrumentNPV(C153,_xll.qlInstrumentSetPricingEngine(C153,C152))</f>
-        <v>6.1556777122901405</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6.1556777122901485</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
       <c r="A157" s="5" t="s">
         <v>211</v>
       </c>
@@ -4057,15 +4046,15 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB3F7D0-4BDF-422B-8B4A-B8A57ABB0447}">
   <dimension ref="A1:D116"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="27.375" customWidth="1"/>
+    <col min="4" max="4" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -4073,7 +4062,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4081,7 +4070,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4090,7 +4079,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -4099,7 +4088,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4108,7 +4097,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4117,7 +4106,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -4126,7 +4115,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4135,7 +4124,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -4152,7 +4141,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>212</v>
       </c>
@@ -4166,7 +4155,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>213</v>
       </c>
@@ -4177,7 +4166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>214</v>
       </c>
@@ -4185,7 +4174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>215</v>
       </c>
@@ -4193,7 +4182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>216</v>
       </c>
@@ -4201,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>217</v>
       </c>
@@ -4212,7 +4201,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>218</v>
       </c>
@@ -4223,7 +4212,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>219</v>
       </c>
@@ -4231,7 +4220,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>220</v>
       </c>
@@ -4239,7 +4228,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15">
       <c r="A22" s="10" t="s">
         <v>222</v>
       </c>
@@ -4256,7 +4245,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R22C4MCLDEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -4273,13 +4262,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R23C4VanillaOption,A</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>44</v>
       </c>
       <c r="B24" cm="1">
         <f t="array" ref="B24">_xll.qlInstrumentNPV(B23,_xll.qlInstrumentSetPricingEngine(B23,B22))</f>
-        <v>8.7097224309098475</v>
+        <v>8.8553369333723371</v>
       </c>
       <c r="C24" cm="1">
         <f t="array" ref="C24">_xll.qlInstrumentNPV(C23,_xll.qlInstrumentSetPricingEngine(C23,C22))</f>
@@ -4290,7 +4279,7 @@
         <v>9.2026950227235051</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>164</v>
       </c>
@@ -4307,7 +4296,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>212</v>
       </c>
@@ -4321,7 +4310,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -4332,7 +4321,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -4340,7 +4329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>216</v>
       </c>
@@ -4348,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>223</v>
       </c>
@@ -4356,7 +4345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>217</v>
       </c>
@@ -4367,7 +4356,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>218</v>
       </c>
@@ -4378,7 +4367,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -4386,7 +4375,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>220</v>
       </c>
@@ -4394,7 +4383,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>224</v>
       </c>
@@ -4402,7 +4391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>225</v>
       </c>
@@ -4410,7 +4399,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>226</v>
       </c>
@@ -4418,7 +4407,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>227</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>228</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="15">
       <c r="A43" s="10" t="s">
         <v>229</v>
       </c>
@@ -4451,7 +4440,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R43C4MCLDAmericanEngine,A</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -4468,13 +4457,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R44C4VanillaOption,A</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>44</v>
       </c>
       <c r="B45" cm="1">
         <f t="array" ref="B45">_xll.qlInstrumentNPV(B44,_xll.qlInstrumentSetPricingEngine(B44,B43))</f>
-        <v>9.1847440240848908</v>
+        <v>9.0373668859801874</v>
       </c>
       <c r="C45" cm="1">
         <f t="array" ref="C45">_xll.qlInstrumentNPV(C44,_xll.qlInstrumentSetPricingEngine(C44,C43))</f>
@@ -4485,7 +4474,7 @@
         <v>9.5427761104331701</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>164</v>
       </c>
@@ -4502,7 +4491,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -4516,7 +4505,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>213</v>
       </c>
@@ -4527,7 +4516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -4535,7 +4524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>215</v>
       </c>
@@ -4543,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>216</v>
       </c>
@@ -4551,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>217</v>
       </c>
@@ -4562,7 +4551,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -4573,7 +4562,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>219</v>
       </c>
@@ -4581,7 +4570,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>220</v>
       </c>
@@ -4589,7 +4578,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="15">
       <c r="A59" s="10" t="s">
         <v>231</v>
       </c>
@@ -4606,7 +4595,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R59C4MCLDDigitalEngine,A</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -4623,13 +4612,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R60C4VanillaOption,A</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>44</v>
       </c>
       <c r="B61" cm="1">
         <f t="array" ref="B61">_xll.qlInstrumentNPV(B60,_xll.qlInstrumentSetPricingEngine(B60,B59))</f>
-        <v>38.991871284032172</v>
+        <v>40.162409262887948</v>
       </c>
       <c r="C61" cm="1">
         <f t="array" ref="C61">_xll.qlInstrumentNPV(C60,_xll.qlInstrumentSetPricingEngine(C60,C59))</f>
@@ -4640,7 +4629,7 @@
         <v>39.710387370649997</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>103</v>
       </c>
@@ -4648,7 +4637,7 @@
         <v>0.19504877171446253</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>104</v>
       </c>
@@ -4656,7 +4645,7 @@
         <v>0.39716005835063128</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -4664,7 +4653,7 @@
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>106</v>
       </c>
@@ -4672,7 +4661,7 @@
         <v>1.3901714719854346</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>107</v>
       </c>
@@ -4680,7 +4669,7 @@
         <v>-0.3506856326404631</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>108</v>
       </c>
@@ -4688,7 +4677,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="15">
       <c r="A70" s="10" t="s">
         <v>110</v>
       </c>
@@ -4697,7 +4686,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>164</v>
       </c>
@@ -4714,7 +4703,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>212</v>
       </c>
@@ -4728,7 +4717,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>213</v>
       </c>
@@ -4739,7 +4728,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>214</v>
       </c>
@@ -4747,7 +4736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>216</v>
       </c>
@@ -4755,7 +4744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>217</v>
       </c>
@@ -4766,7 +4755,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>218</v>
       </c>
@@ -4777,7 +4766,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>219</v>
       </c>
@@ -4785,7 +4774,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>220</v>
       </c>
@@ -4793,7 +4782,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="15">
       <c r="A82" s="10" t="s">
         <v>232</v>
       </c>
@@ -4810,7 +4799,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R82C4MCLDEuropeanHestonEngine,A</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -4827,13 +4816,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R83C4VanillaOption,A</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>44</v>
       </c>
       <c r="B84" cm="1">
         <f t="array" ref="B84">_xll.qlInstrumentNPV(B83,_xll.qlInstrumentSetPricingEngine(B83,B82))</f>
-        <v>11.453484861858684</v>
+        <v>11.726886532746791</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">_xll.qlInstrumentNPV(C83,_xll.qlInstrumentSetPricingEngine(C83,C82))</f>
@@ -4844,7 +4833,7 @@
         <v>12.243422822818205</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>164</v>
       </c>
@@ -4861,7 +4850,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>212</v>
       </c>
@@ -4875,7 +4864,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>213</v>
       </c>
@@ -4886,7 +4875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>214</v>
       </c>
@@ -4894,7 +4883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>215</v>
       </c>
@@ -4902,7 +4891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>216</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>217</v>
       </c>
@@ -4921,7 +4910,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>218</v>
       </c>
@@ -4932,7 +4921,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>219</v>
       </c>
@@ -4940,7 +4929,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>220</v>
       </c>
@@ -4948,7 +4937,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="15">
       <c r="A98" s="10" t="s">
         <v>233</v>
       </c>
@@ -4965,7 +4954,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R98C4MCLDForwardEuropeanBSEngine,A</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>39</v>
       </c>
@@ -4982,13 +4971,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R99C4ForwardVanillaOption,A</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>44</v>
       </c>
       <c r="B100" cm="1">
         <f t="array" ref="B100">_xll.qlInstrumentNPV(B99,_xll.qlInstrumentSetPricingEngine(B99,B98))</f>
-        <v>6.6298105133204537</v>
+        <v>6.8313783268773243</v>
       </c>
       <c r="C100" cm="1">
         <f t="array" ref="C100">_xll.qlInstrumentNPV(C99,_xll.qlInstrumentSetPricingEngine(C99,C98))</f>
@@ -4999,7 +4988,7 @@
         <v>6.6472484436112005</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>164</v>
       </c>
@@ -5016,7 +5005,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>212</v>
       </c>
@@ -5030,7 +5019,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -5041,7 +5030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -5049,7 +5038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>216</v>
       </c>
@@ -5057,7 +5046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -5068,7 +5057,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -5079,7 +5068,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>219</v>
       </c>
@@ -5087,7 +5076,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>220</v>
       </c>
@@ -5095,7 +5084,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -5103,7 +5092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="15">
       <c r="A114" s="10" t="s">
         <v>234</v>
       </c>
@@ -5120,7 +5109,7 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R114C4MCLDForwardEuropeanHestonEngine,A</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>39</v>
       </c>
@@ -5137,13 +5126,13 @@
         <v>欣[test_options.xlsx]Monte Carlo engines!R115C4ForwardVanillaOption,A</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>44</v>
       </c>
       <c r="B116" cm="1">
         <f t="array" ref="B116">_xll.qlInstrumentNPV(B115,_xll.qlInstrumentSetPricingEngine(B115,B114))</f>
-        <v>4.7860243594808889</v>
+        <v>4.6939409970313122</v>
       </c>
       <c r="C116" cm="1">
         <f t="array" ref="C116">_xll.qlInstrumentNPV(C115,_xll.qlInstrumentSetPricingEngine(C115,C114))</f>
@@ -5162,13 +5151,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB17C3C-4879-44BA-9C70-2EC65C34CDC4}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.109375" customWidth="1"/>
-    <col min="2" max="3" width="22.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28.125" customWidth="1"/>
+    <col min="2" max="3" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -5176,7 +5165,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5184,7 +5173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>欣[test_options.xlsx]QD engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -5202,7 +5191,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -5211,7 +5200,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5220,7 +5209,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5229,7 +5218,7 @@
         <v>欣[test_options.xlsx]QD engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -5238,7 +5227,7 @@
         <v>欣[test_options.xlsx]QD engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -5251,7 +5240,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -5259,7 +5248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>236</v>
       </c>
@@ -5267,7 +5256,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>237</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>238</v>
       </c>
@@ -5283,7 +5272,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="15">
       <c r="A17" s="10" t="s">
         <v>239</v>
       </c>
@@ -5296,7 +5285,7 @@
         <v>欣[test_options.xlsx]QD engines!R17C3QdPlusAmericanEngine,A</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -5309,7 +5298,7 @@
         <v>欣[test_options.xlsx]QD engines!R18C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -5322,7 +5311,7 @@
         <v>9.3496944863644025</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>164</v>
       </c>
@@ -5335,7 +5324,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>241</v>
       </c>
@@ -5343,7 +5332,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>242</v>
       </c>
@@ -5351,7 +5340,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="15">
       <c r="A26" s="10" t="s">
         <v>239</v>
       </c>
@@ -5364,7 +5353,7 @@
         <v>欣[test_options.xlsx]QD engines!R26C3QdFpAmericanEngine,A</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -5377,7 +5366,7 @@
         <v>欣[test_options.xlsx]QD engines!R27C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -5398,13 +5387,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9C449D-D6B9-4CF1-B388-CB98F726ED30}">
   <dimension ref="A1:C77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="3" width="26.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="3" width="26.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -5412,7 +5401,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5420,7 +5409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5429,7 +5418,7 @@
         <v>欣[test_options.xlsx]Other engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -5438,7 +5427,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -5447,7 +5436,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5456,7 +5445,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5465,7 +5454,7 @@
         <v>欣[test_options.xlsx]Other engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -5474,7 +5463,7 @@
         <v>欣[test_options.xlsx]Other engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>205</v>
       </c>
@@ -5482,7 +5471,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -5490,7 +5479,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>206</v>
       </c>
@@ -5498,7 +5487,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>246</v>
       </c>
@@ -5516,7 +5505,7 @@
         <v>欣[test_options.xlsx]Other engines!R16C2AnalyticCEVEngine,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -5525,7 +5514,7 @@
         <v>欣[test_options.xlsx]Other engines!R17C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -5534,12 +5523,12 @@
         <v>6.1006434414802895</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -5547,7 +5536,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -5555,7 +5544,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -5563,7 +5552,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -5571,7 +5560,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -5579,7 +5568,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>193</v>
       </c>
@@ -5587,7 +5576,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>194</v>
       </c>
@@ -5595,7 +5584,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>195</v>
       </c>
@@ -5603,7 +5592,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="15">
       <c r="A30" s="10" t="s">
         <v>196</v>
       </c>
@@ -5612,7 +5601,7 @@
         <v>欣[test_options.xlsx]Other engines!R30C2BatesProcess,A</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>201</v>
       </c>
@@ -5625,7 +5614,7 @@
         <v>欣[test_options.xlsx]Other engines!R33C3BatesModel,A</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>121</v>
       </c>
@@ -5633,7 +5622,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -5641,7 +5630,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -5649,7 +5638,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="15">
       <c r="A37" s="10" t="s">
         <v>247</v>
       </c>
@@ -5662,7 +5651,7 @@
         <v>欣[test_options.xlsx]Other engines!R37C3BatesEngine,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -5675,7 +5664,7 @@
         <v>欣[test_options.xlsx]Other engines!R38C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -5688,7 +5677,7 @@
         <v>7.2863190675642429</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -5697,7 +5686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>250</v>
       </c>
@@ -5706,7 +5695,7 @@
         <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>249</v>
       </c>
@@ -5715,7 +5704,7 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>106</v>
       </c>
@@ -5723,7 +5712,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -5731,7 +5720,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
@@ -5739,7 +5728,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="15">
       <c r="A48" s="10" t="s">
         <v>248</v>
       </c>
@@ -5748,7 +5737,7 @@
         <v>欣[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="15">
       <c r="A50" s="10" t="s">
         <v>251</v>
       </c>
@@ -5757,7 +5746,7 @@
         <v>欣[test_options.xlsx]Other engines!R50C2VarianceGammaEngine,A</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -5766,7 +5755,7 @@
         <v>欣[test_options.xlsx]Other engines!R51C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -5775,7 +5764,7 @@
         <v>7.1734102119479957</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -5788,7 +5777,7 @@
         <v>欣[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>252</v>
       </c>
@@ -5797,7 +5786,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="15">
       <c r="A57" s="10" t="s">
         <v>253</v>
       </c>
@@ -5810,7 +5799,7 @@
         <v>欣[test_options.xlsx]Other engines!R57C3FFTVarianceGammaEngine,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -5823,7 +5812,7 @@
         <v>欣[test_options.xlsx]Other engines!R58C3VanillaOption,A</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>44</v>
       </c>
@@ -5836,7 +5825,7 @@
         <v>7.1223043890456808</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>249</v>
       </c>
@@ -5845,7 +5834,7 @@
         <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>250</v>
       </c>
@@ -5854,7 +5843,7 @@
         <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -5863,7 +5852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>103</v>
       </c>
@@ -5871,7 +5860,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>254</v>
       </c>
@@ -5879,7 +5868,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>140</v>
       </c>
@@ -5887,7 +5876,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>206</v>
       </c>
@@ -5895,7 +5884,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>255</v>
       </c>
@@ -5903,7 +5892,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -5911,7 +5900,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>256</v>
       </c>
@@ -5919,7 +5908,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>108</v>
       </c>
@@ -5927,7 +5916,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="15">
       <c r="A72" s="10" t="s">
         <v>257</v>
       </c>
@@ -5936,7 +5925,7 @@
         <v>欣[test_options.xlsx]Other engines!R72C2GJRGARCHProcess,A</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>258</v>
       </c>
@@ -5945,7 +5934,7 @@
         <v>欣[test_options.xlsx]Other engines!R74C2GJRGARCHModel,A</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="15">
       <c r="A75" s="14" t="s">
         <v>259</v>
       </c>
@@ -5954,7 +5943,7 @@
         <v>欣[test_options.xlsx]Other engines!R75C2AnalyticGJRGARCHEngine,A</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -5963,7 +5952,7 @@
         <v>欣[test_options.xlsx]Other engines!R76C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -5980,13 +5969,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08B26FA-D774-49D0-B70E-4BE5D6D689B9}">
   <dimension ref="A2:B61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5994,7 +5983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6002,7 +5991,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6011,7 +6000,7 @@
         <v>欣[test_options.xlsx]Calculators!R4C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>260</v>
       </c>
@@ -6019,7 +6008,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>269</v>
       </c>
@@ -6027,7 +6016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>0.35355339059327379</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>262</v>
       </c>
@@ -6044,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="15">
       <c r="A9" s="10" t="s">
         <v>263</v>
       </c>
@@ -6053,7 +6042,7 @@
         <v>欣[test_options.xlsx]Calculators!R9C2BlackCalculator,A</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>264</v>
       </c>
@@ -6062,7 +6051,7 @@
         <v>14.031620480133384</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>265</v>
       </c>
@@ -6071,7 +6060,7 @@
         <v>0.57015810240066678</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>266</v>
       </c>
@@ -6080,7 +6069,7 @@
         <v>1.1108852695966624E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>267</v>
       </c>
@@ -6089,7 +6078,7 @@
         <v>39.275725362602309</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>268</v>
       </c>
@@ -6098,7 +6087,7 @@
         <v>-3.4715164674895713</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>270</v>
       </c>
@@ -6107,7 +6096,7 @@
         <v>-9.5110040205193726E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>271</v>
       </c>
@@ -6116,7 +6105,7 @@
         <v>42.984189759933301</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>272</v>
       </c>
@@ -6125,7 +6114,7 @@
         <v>-57.015810240066685</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>273</v>
       </c>
@@ -6134,7 +6123,7 @@
         <v>0.57015810240066678</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>274</v>
       </c>
@@ -6143,7 +6132,7 @@
         <v>1.1108852695966624E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>275</v>
       </c>
@@ -6152,7 +6141,7 @@
         <v>4.0633803002862203</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>276</v>
       </c>
@@ -6161,7 +6150,7 @@
         <v>4.0633803002862203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>277</v>
       </c>
@@ -6170,7 +6159,7 @@
         <v>0.42984189759933311</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>278</v>
       </c>
@@ -6179,7 +6168,7 @@
         <v>0.57015810240066689</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>279</v>
       </c>
@@ -6188,7 +6177,7 @@
         <v>-0.42984189759933311</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>280</v>
       </c>
@@ -6197,7 +6186,7 @@
         <v>1.1108852695966624E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>281</v>
       </c>
@@ -6206,7 +6195,7 @@
         <v>0.57015810240066689</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>282</v>
       </c>
@@ -6215,7 +6204,7 @@
         <v>0.27772131739916567</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>283</v>
       </c>
@@ -6224,7 +6213,7 @@
         <v>-3.4715164674895709</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>284</v>
       </c>
@@ -6233,7 +6222,7 @@
         <v>-0.42984189759933311</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -6241,7 +6230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -6249,7 +6238,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -6258,7 +6247,7 @@
         <v>欣[test_options.xlsx]Calculators!R35C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>260</v>
       </c>
@@ -6266,7 +6255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>269</v>
       </c>
@@ -6274,7 +6263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>261</v>
       </c>
@@ -6283,7 +6272,7 @@
         <v>35.355339059327378</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>262</v>
       </c>
@@ -6291,7 +6280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="15">
       <c r="A40" s="10" t="s">
         <v>305</v>
       </c>
@@ -6300,7 +6289,7 @@
         <v>欣[test_options.xlsx]Calculators!R40C2BachelierCalculator,A</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>285</v>
       </c>
@@ -6309,7 +6298,7 @@
         <v>14.104739588693908</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>286</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>287</v>
       </c>
@@ -6327,7 +6316,7 @@
         <v>1.1283791670955126E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>288</v>
       </c>
@@ -6336,7 +6325,7 @@
         <v>0.3989422804014327</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>289</v>
       </c>
@@ -6345,7 +6334,7 @@
         <v>-3.5261848971734771</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>290</v>
       </c>
@@ -6354,7 +6343,7 @@
         <v>-9.6607805402013063E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>291</v>
       </c>
@@ -6363,7 +6352,7 @@
         <v>35.89526041130609</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>292</v>
       </c>
@@ -6372,7 +6361,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>293</v>
       </c>
@@ -6381,7 +6370,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>294</v>
       </c>
@@ -6390,7 +6379,7 @@
         <v>1.1283791670955126E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>295</v>
       </c>
@@ -6399,7 +6388,7 @@
         <v>3.5449077018110322</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>296</v>
       </c>
@@ -6408,7 +6397,7 @@
         <v>3.5449077018110322</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>297</v>
       </c>
@@ -6417,7 +6406,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>298</v>
       </c>
@@ -6426,7 +6415,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>299</v>
       </c>
@@ -6435,7 +6424,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>300</v>
       </c>
@@ -6444,7 +6433,7 @@
         <v>1.1283791670955126E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>301</v>
       </c>
@@ -6453,7 +6442,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>302</v>
       </c>
@@ -6462,7 +6451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>303</v>
       </c>
@@ -6471,7 +6460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>304</v>
       </c>
@@ -6488,13 +6477,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D4C454-6496-4030-9322-588925AFA751}">
   <dimension ref="A2:C21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>195</v>
       </c>
@@ -6502,7 +6491,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>306</v>
       </c>
@@ -6510,7 +6499,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>307</v>
       </c>
@@ -6518,7 +6507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>308</v>
       </c>
@@ -6526,7 +6515,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" s="10" t="s">
         <v>311</v>
       </c>
@@ -6535,7 +6524,7 @@
         <v>欣[test_options.xlsx]DeltaVolQuote!R6C2DeltaVolQuote,A</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>306</v>
       </c>
@@ -6543,7 +6532,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>308</v>
       </c>
@@ -6551,7 +6540,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>307</v>
       </c>
@@ -6559,7 +6548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>309</v>
       </c>
@@ -6567,7 +6556,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15">
       <c r="A13" s="10" t="s">
         <v>313</v>
       </c>
@@ -6576,7 +6565,7 @@
         <v>欣[test_options.xlsx]DeltaVolQuote!R13C2DeltaVolQuote,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="B15" s="3" t="s">
         <v>320</v>
       </c>
@@ -6584,7 +6573,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>314</v>
       </c>
@@ -6594,10 +6583,10 @@
       </c>
       <c r="C16" cm="1">
         <f t="array" ref="C16">_xll.qlDeltaVolQuoteDelta($B$13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.447659336600622E-307</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>315</v>
       </c>
@@ -6610,7 +6599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>316</v>
       </c>
@@ -6623,7 +6612,7 @@
         <v>FWD</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>317</v>
       </c>
@@ -6636,7 +6625,7 @@
         <v>ATMDELTANEUTRAL</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>318</v>
       </c>
@@ -6649,7 +6638,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>319</v>
       </c>
@@ -6670,16 +6659,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ECC675-21D6-4AF3-8CED-1A0276C20E9A}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="42.21875" customWidth="1"/>
-    <col min="5" max="5" width="30.88671875" customWidth="1"/>
+    <col min="4" max="4" width="42.25" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -6687,7 +6676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6695,7 +6684,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -6704,7 +6693,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -6713,7 +6702,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6722,7 +6711,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6731,7 +6720,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6740,7 +6729,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -6749,7 +6738,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R9C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -6760,7 +6749,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6778,7 +6767,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6795,7 +6784,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R13C4ForwardEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6812,7 +6801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -6829,12 +6818,12 @@
         <v>7.1837456553616867</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -6851,7 +6840,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R18C4Payoff,A</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -6868,12 +6857,12 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R19C4Exercise,A</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -6886,7 +6875,7 @@
         <v>7.1837456553616924E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -6895,7 +6884,7 @@
         <v>0.54881413040339544</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -6904,7 +6893,7 @@
         <v>5.435919456400006</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -6917,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -6930,7 +6919,7 @@
         <v>0.14367491310723376</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -6939,7 +6928,7 @@
         <v>-1.3891369564089494E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -6952,7 +6941,7 @@
         <v>27.648221450537704</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -6965,7 +6954,7 @@
         <v>23.52246414275961</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -6978,7 +6967,7 @@
         <v>-30.706209798121296</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -6987,7 +6976,7 @@
         <v>-0.45235445135748031</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -6996,12 +6985,12 @@
         <v>0.46613069535537099</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -7014,7 +7003,7 @@
         <v>0.25021417501222348</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -7023,7 +7012,7 @@
         <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R37C2IntegralEngine,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -7032,7 +7021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="B39" cm="1">
         <f t="array" ref="B39">_xll.qlInstrumentNPV(B12,B38)</f>
         <v>10.197536883163878</v>
@@ -7046,14 +7035,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CE4A13-30A4-4450-A74A-F560395BF07F}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.21875" customWidth="1"/>
-    <col min="2" max="3" width="29.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.25" customWidth="1"/>
+    <col min="2" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -7061,7 +7050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7069,7 +7058,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -7078,7 +7067,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7087,7 +7076,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -7096,7 +7085,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R5C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>90</v>
       </c>
@@ -7112,7 +7101,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R7C4FixedDividend,A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -7128,10 +7117,10 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R8C4FixedDividend,A</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -7144,7 +7133,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R10C3EuropeanOption,A</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15">
       <c r="A11" s="10" t="s">
         <v>92</v>
       </c>
@@ -7157,7 +7146,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R11C3AnalyticDividendEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -7170,7 +7159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -7183,7 +7172,7 @@
         <v>9.3855010920597781</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -7196,7 +7185,7 @@
         <v>0.25000065354450668</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -7209,7 +7198,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R18C3EuropeanOption,A</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -7220,7 +7209,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="15">
       <c r="A20" s="10" t="s">
         <v>95</v>
       </c>
@@ -7233,7 +7222,7 @@
         <v>欣[test_options.xlsx]Cash dividend engines!R20C3CashDividendEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -7246,7 +7235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -7259,7 +7248,7 @@
         <v>9.4216741335272367</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -7280,13 +7269,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754ED873-FE9B-4DF0-A6E1-3DE4D694F510}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="2" max="2" width="29.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -7294,7 +7283,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7302,7 +7291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -7311,7 +7300,7 @@
         <v>欣[test_options.xlsx]American option engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -7320,7 +7309,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7329,7 +7318,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -7338,7 +7327,7 @@
         <v>欣[test_options.xlsx]American option engines!R7C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -7347,7 +7336,7 @@
         <v>欣[test_options.xlsx]American option engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -7356,7 +7345,7 @@
         <v>欣[test_options.xlsx]American option engines!R10C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="15">
       <c r="A11" s="10" t="s">
         <v>99</v>
       </c>
@@ -7365,7 +7354,7 @@
         <v>欣[test_options.xlsx]American option engines!R11C2AnalyticEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -7374,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -7383,7 +7372,7 @@
         <v>9.2222212996374502</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -7392,7 +7381,7 @@
         <v>欣[test_options.xlsx]American option engines!R15C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="15">
       <c r="A16" s="10" t="s">
         <v>96</v>
       </c>
@@ -7401,7 +7390,7 @@
         <v>欣[test_options.xlsx]American option engines!R16C2BaroneAdesiWhaleyApproximationEngine,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -7410,7 +7399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -7419,7 +7408,7 @@
         <v>9.3532072716898096</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -7428,7 +7417,7 @@
         <v>欣[test_options.xlsx]American option engines!R20C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="15">
       <c r="A21" s="10" t="s">
         <v>97</v>
       </c>
@@ -7437,7 +7426,7 @@
         <v>欣[test_options.xlsx]American option engines!R21C2BjerksundStenslandApproximationEngine,A</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -7446,7 +7435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -7455,7 +7444,7 @@
         <v>9.3071138760570022</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -7464,7 +7453,7 @@
         <v>欣[test_options.xlsx]American option engines!R25C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="15">
       <c r="A26" s="10" t="s">
         <v>100</v>
       </c>
@@ -7473,7 +7462,7 @@
         <v>欣[test_options.xlsx]American option engines!R26C2JuQuadraticApproximationEngine,A</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -7482,7 +7471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -7491,7 +7480,7 @@
         <v>9.3291840238072936</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -7500,7 +7489,7 @@
         <v>欣[test_options.xlsx]American option engines!R30C2CashOrNothingPayoff,A</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -7509,7 +7498,7 @@
         <v>欣[test_options.xlsx]American option engines!R32C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="15">
       <c r="A33" s="10" t="s">
         <v>99</v>
       </c>
@@ -7518,7 +7507,7 @@
         <v>欣[test_options.xlsx]American option engines!R33C2AnalyticEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -7527,7 +7516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -7536,7 +7525,7 @@
         <v>20.347124841370352</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -7545,7 +7534,7 @@
         <v>欣[test_options.xlsx]American option engines!R37C2VanillaOption,A</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="15">
       <c r="A38" s="10" t="s">
         <v>102</v>
       </c>
@@ -7554,7 +7543,7 @@
         <v>欣[test_options.xlsx]American option engines!R38C2AnalyticDigitalAmericanEngine,A</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -7563,7 +7552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -7580,13 +7569,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5429400-C69B-40A4-97DF-D86E663593B9}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="36.33203125" customWidth="1"/>
+    <col min="2" max="3" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -7594,7 +7583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7602,16 +7591,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="str" cm="1">
+      <c r="B3" t="str">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
         <v>欣[test_options.xlsx]Quanto options!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -7620,7 +7609,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -7629,7 +7618,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7638,16 +7627,16 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="str" cm="1">
+      <c r="B8" t="str">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
         <v>欣[test_options.xlsx]Quanto options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15">
       <c r="B10" s="6" t="s">
         <v>40</v>
       </c>
@@ -7655,38 +7644,38 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2" t="str" cm="1">
+      <c r="B11" s="2" t="str">
         <f t="array" ref="B11">_xll.qlQuantoVanillaOption(B3,B8)</f>
         <v>欣[test_options.xlsx]Quanto options!R11C2QuantoVanillaOption,A</v>
       </c>
-      <c r="C11" s="2" t="str" cm="1">
+      <c r="C11" s="2" t="str">
         <f t="array" ref="C11">_xll.qlQuantoForwardVanillaOption(1,B5,B3,B8)</f>
         <v>欣[test_options.xlsx]Quanto options!R11C3QuantoForwardVanillaOption,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13">_xll.qlFlatForward(EvaluationDate,0.04)</f>
+      <c r="B13" t="str">
+        <f>_xll.qlFlatForward(EvaluationDate,0.04,"actual365fixed")</f>
         <v>欣[test_options.xlsx]Quanto options!R13C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="str" cm="1">
+      <c r="B14" t="str">
         <f t="array" ref="B14">_xll.qlBlackConstantVol(EvaluationDate,"NullCalendar",0.15,"Act/365")</f>
         <v>欣[test_options.xlsx]Quanto options!R14C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>185</v>
       </c>
@@ -7694,152 +7683,152 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2" t="str" cm="1">
+      <c r="B16" s="2" t="str">
         <f t="array" ref="B16">_xll.qlQuantoEuropeanEngine(BlackScholesProcess,B13,B14,B15)</f>
         <v>欣[test_options.xlsx]Quanto options!R16C2QuantoEuropeanEngine,A</v>
       </c>
-      <c r="C16" t="str" cm="1">
+      <c r="C16" t="str">
         <f t="array" ref="C16">_xll.qlQuantoForwardEuropeanEngine(BlackScholesProcess,B13,B14,B15)</f>
         <v>欣[test_options.xlsx]Quanto options!R16C3QuantoForwardEuropeanEngine,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="b" cm="1">
+      <c r="B17" t="b">
         <f t="array" ref="B17">_xll.qlInstrumentSetPricingEngine(B11,B16)</f>
         <v>1</v>
       </c>
-      <c r="C17" t="b" cm="1">
+      <c r="C17" t="b">
         <f t="array" ref="C17">_xll.qlInstrumentSetPricingEngine(C11,C16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" cm="1">
+      <c r="B18">
         <f t="array" ref="B18">_xll.qlInstrumentNPV(B11,B17)</f>
         <v>11.878888587119283</v>
       </c>
-      <c r="C18" s="5" cm="1">
+      <c r="C18" s="5">
         <f t="array" ref="C18">FIND("RuntimeError: RuntimeError: wrong engine type",_xll.qlInstrumentNPV(C11,C17))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
-      <c r="B21" cm="1">
+      <c r="B21">
         <f t="array" ref="B21">_xll.qlOneAssetOptionDelta(B11,B17)</f>
         <v>0.61562446332249943</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
-      <c r="B24" cm="1">
+      <c r="B24">
         <f t="array" ref="B24">_xll.qlOneAssetOptionGamma(B11,B17)</f>
         <v>1.5479103002523637E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" cm="1">
+      <c r="B25">
         <f t="array" ref="B25">_xll.qlOneAssetOptionTheta(B11,B17)</f>
         <v>-6.8663978260497398</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
-      <c r="B27" cm="1">
+      <c r="B27">
         <f t="array" ref="B27">_xll.qlOneAssetOptionVega(B11,B17)</f>
         <v>43.314940981227871</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B28" cm="1">
+      <c r="B28">
         <f t="array" ref="B28">_xll.qlOneAssetOptionRho(B11,B17)</f>
         <v>-11.878888587119285</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
-      <c r="B29" cm="1">
+      <c r="B29">
         <f t="array" ref="B29">_xll.qlOneAssetOptionDividendRho(B11,B17)</f>
         <v>-61.562446332249941</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>45</v>
       </c>
-      <c r="B33" cm="1">
+      <c r="B33">
         <f t="array" ref="B33">_xll.qlQuantoVanillaOptionQVega(B11,B17)</f>
         <v>7.6953057915312426</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
-      <c r="B34" cm="1">
+      <c r="B34">
         <f t="array" ref="B34">_xll.qlQuantoVanillaOptionQRho(B11,B17)</f>
         <v>61.562446332249941</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
-      <c r="B35" cm="1">
+      <c r="B35">
         <f t="array" ref="B35">_xll.qlQuantoVanillaOptionQLambda(B11,B17)</f>
         <v>-2.3085917374593725</v>
       </c>
@@ -7852,15 +7841,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F6DF5F-2AA3-4198-8307-9EACFAC882BC}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="44.44140625" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="44.5" customWidth="1"/>
+    <col min="4" max="4" width="33.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -7874,7 +7863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -7888,7 +7877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="C3" t="s">
         <v>65</v>
       </c>
@@ -7896,7 +7885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -7905,7 +7894,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -7914,7 +7903,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -7923,7 +7912,7 @@
         <v>欣[test_options.xlsx]Multi-asset options!R6C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -7932,7 +7921,7 @@
         <v>欣[test_options.xlsx]Multi-asset options!R7C2AmericanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15">
       <c r="B9" s="6" t="s">
         <v>51</v>
       </c>
@@ -7943,7 +7932,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="B10" s="2" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlMargrabeOption(B1,B2,B6)</f>
         <v>欣[test_options.xlsx]Multi-asset options!R10C2MargrabeOption,A</v>
@@ -7957,7 +7946,7 @@
         <v>欣[test_options.xlsx]Multi-asset options!R10C4TwoAssetCorrelationOption,A</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -7966,7 +7955,7 @@
         <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -7975,7 +7964,7 @@
         <v>欣[test_options.xlsx]Multi-asset options!R12C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -7983,7 +7972,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -8000,7 +7989,7 @@
         <v>欣[test_options.xlsx]Multi-asset options!R14C4AnalyticTwoAssetCorrelationEngine,A</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8017,7 +8006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -8034,7 +8023,7 @@
         <v>3.7652011408317012</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -8043,7 +8032,7 @@
         <v>0.53885267864448749</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -8052,7 +8041,7 @@
         <v>-0.88269198932453574</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -8061,7 +8050,7 @@
         <v>1.5519983023522328E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -8078,23 +8067,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2B684A-1D00-4688-A2F3-DF6A87D6C7AE}">
   <dimension ref="A2:B78"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" customWidth="1"/>
+    <col min="1" max="1" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15">
       <c r="A2" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -8102,7 +8091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -8110,7 +8099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -8119,7 +8108,7 @@
         <v>欣[test_options.xlsx]Other options!R6C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -8128,7 +8117,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -8137,12 +8126,12 @@
         <v>欣[test_options.xlsx]Other options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -8150,7 +8139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -8158,7 +8147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -8167,7 +8156,7 @@
         <v>欣[test_options.xlsx]Other options!R12C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -8176,7 +8165,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -8185,7 +8174,7 @@
         <v>欣[test_options.xlsx]Other options!R14C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -8194,7 +8183,7 @@
         <v>欣[test_options.xlsx]Other options!R16C2CompoundOption,A</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -8203,7 +8192,7 @@
         <v>欣[test_options.xlsx]Other options!R17C2AnalyticCompoundOptionEngine,A</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -8212,7 +8201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -8221,12 +8210,12 @@
         <v>6.4040752737323103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="15">
       <c r="A22" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -8234,7 +8223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -8243,7 +8232,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -8252,7 +8241,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -8261,7 +8250,7 @@
         <v>欣[test_options.xlsx]Other options!R26C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -8270,7 +8259,7 @@
         <v>欣[test_options.xlsx]Other options!R28C2SimpleChooserOption,A</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -8279,7 +8268,7 @@
         <v>欣[test_options.xlsx]Other options!R29C2AnalyticSimpleChooserEngine,A</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -8288,7 +8277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -8297,12 +8286,12 @@
         <v>16.543209260000324</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="15">
       <c r="A33" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -8310,7 +8299,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -8318,7 +8307,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -8327,7 +8316,7 @@
         <v>46354</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -8336,7 +8325,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -8345,7 +8334,7 @@
         <v>欣[test_options.xlsx]Other options!R38C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -8354,7 +8343,7 @@
         <v>欣[test_options.xlsx]Other options!R40C2ComplexChooserOption,A</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -8363,7 +8352,7 @@
         <v>欣[test_options.xlsx]Other options!R41C2AnalyticComplexChooserEngine,A</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -8372,7 +8361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -8381,12 +8370,12 @@
         <v>6.3126901245785092</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="15">
       <c r="A45" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -8394,7 +8383,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -8402,7 +8391,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -8411,7 +8400,7 @@
         <v>欣[test_options.xlsx]Other options!R48C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -8420,7 +8409,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -8429,12 +8418,12 @@
         <v>欣[test_options.xlsx]Other options!R50C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" s="8" t="s">
         <v>7</v>
       </c>
@@ -8442,7 +8431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" s="8" t="s">
         <v>82</v>
       </c>
@@ -8450,7 +8439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" s="8" t="s">
         <v>83</v>
       </c>
@@ -8459,7 +8448,7 @@
         <v>46904</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" s="8" t="s">
         <v>8</v>
       </c>
@@ -8467,7 +8456,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -8476,7 +8465,7 @@
         <v>欣[test_options.xlsx]Other options!R57C2HolderExtensibleOption,A</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -8485,7 +8474,7 @@
         <v>欣[test_options.xlsx]Other options!R58C2AnalyticHolderExtensibleOptionEngine,A</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -8494,7 +8483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>44</v>
       </c>
@@ -8503,12 +8492,12 @@
         <v>11.139249894545387</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="15">
       <c r="A62" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -8516,7 +8505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -8524,7 +8513,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -8533,7 +8522,7 @@
         <v>欣[test_options.xlsx]Other options!R65C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>60</v>
       </c>
@@ -8542,7 +8531,7 @@
         <v>46539</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -8551,12 +8540,12 @@
         <v>欣[test_options.xlsx]Other options!R67C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" s="8" t="s">
         <v>7</v>
       </c>
@@ -8564,7 +8553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" s="8" t="s">
         <v>8</v>
       </c>
@@ -8572,7 +8561,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" s="8" t="s">
         <v>10</v>
       </c>
@@ -8581,7 +8570,7 @@
         <v>欣[test_options.xlsx]Other options!R71C2PlainVanillaPayoff,A</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" s="8" t="s">
         <v>60</v>
       </c>
@@ -8590,7 +8579,7 @@
         <v>46904</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" s="8" t="s">
         <v>13</v>
       </c>
@@ -8599,7 +8588,7 @@
         <v>欣[test_options.xlsx]Other options!R73C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -8608,7 +8597,7 @@
         <v>欣[test_options.xlsx]Other options!R75C2WriterExtensibleOption,A</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v>欣[test_options.xlsx]Other options!R76C2AnalyticWriterExtensibleOptionEngine,A</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>62</v>
       </c>
@@ -8626,7 +8615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>44</v>
       </c>
